--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127008809</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B7" t="n">
-        <v>92535</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1263,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,49 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,6 +1374,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127008809</v>
       </c>
       <c r="B5" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,49 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>92615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R7" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,45 +1287,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B8" t="n">
-        <v>92609</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R8" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1375,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1184,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B7" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1263,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,49 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,6 +1374,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1184,49 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R7" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,45 +1287,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B8" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R8" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1375,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127008805</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127008809</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127008808</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>127008811</v>
       </c>
       <c r="B7" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127008813</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1184,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1263,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,49 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,6 +1374,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,6 +1391,727 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127669618</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>500m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>686291</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7282051</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127669528</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>686299</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7282083</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127669906</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>686599</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7282017</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127669651</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>500m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>686289</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7282027</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127669842</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>686599</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7282017</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127669857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>686599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7282017</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127670013</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>686544</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7282153</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1184,49 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R7" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,45 +1287,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R8" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1375,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,27 +1608,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,7 +1688,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1801,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669842</v>
+        <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>56853</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,35 +1819,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127008805</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127008809</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127008808</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1263,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,49 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,6 +1374,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,6 +2112,2304 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127734510</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78687</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>686360</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7282102</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127734354</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79638</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>686355</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7282009</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127734327</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79638</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7282026</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127734555</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79638</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>686452</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7282287</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127734518</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78778</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>686386</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7282202</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127734420</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>686309</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7282011</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Den kvarvarande naturskogsresten är lämplig tjäderbiotop och tjäderhonan är troligen stationär i området. Dessutom är miljön kring källbäcken lämpligt för häckning och uppfödande av tjäderkycklingar.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127734344</v>
+      </c>
+      <c r="B22" t="n">
+        <v>77998</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7282024</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127734553</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78778</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>686452</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7282287</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127734607</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91493</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>686468</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7282322</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127734349</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>686355</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7282009</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127734329</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78778</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7282026</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127734640</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57767</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>686342</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7281946</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En familjegrupp med 4 fåglar</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127734894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>686422</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7282062</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127734522</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78687</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>686386</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7282202</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127734519</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79638</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686386</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7282202</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127734610</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79099</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>864</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686467</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7282303</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127734256</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79638</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>686373</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7282022</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127734539</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91493</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>686419</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7282238</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127734343</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7282024</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127734602</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>686476</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7282298</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127734251</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92626</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>686434</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7282004</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127734493</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>686286</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7282001</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1184,49 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R7" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,45 +1287,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R8" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1375,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B24" t="n">
-        <v>91493</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R24" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>91493</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R25" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>78687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,43 +3367,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3411,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R28" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3449,17 +3432,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,26 +3468,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3516,10 +3512,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R29" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3554,13 +3550,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79638</v>
+        <v>79099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R30" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79099</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R31" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734256</v>
+        <v>127734343</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,26 +3792,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3819,10 +3836,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686373</v>
+        <v>686366</v>
       </c>
       <c r="R32" t="n">
-        <v>7282022</v>
+        <v>7282024</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3863,7 +3880,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3882,32 +3898,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B33" t="n">
-        <v>91493</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3936,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R33" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3983,54 +3999,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>91493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4038,10 +4037,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R34" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4082,6 +4081,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4100,42 +4100,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734602</v>
+        <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>92626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686476</v>
+        <v>686434</v>
       </c>
       <c r="R35" t="n">
-        <v>7282298</v>
+        <v>7282004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4187,6 +4182,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4205,37 +4201,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734251</v>
+        <v>127734602</v>
       </c>
       <c r="B36" t="n">
-        <v>92626</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4243,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686434</v>
+        <v>686476</v>
       </c>
       <c r="R36" t="n">
-        <v>7282004</v>
+        <v>7282298</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4287,7 +4288,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B11" t="n">
-        <v>56855</v>
+        <v>97327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,46 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1688,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>97327</v>
+        <v>98471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1734,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,27 +1812,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669651</v>
+        <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>97327</v>
+        <v>56855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,38 +1608,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R11" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1680,7 +1688,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669906</v>
+        <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>98471</v>
+        <v>97327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1734,14 +1741,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R12" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1801,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669842</v>
+        <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,35 +1819,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B28" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,26 +3367,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3394,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R28" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3432,13 +3449,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3457,10 +3478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>78687</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,43 +3489,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3512,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R29" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3550,17 +3554,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B30" t="n">
-        <v>79099</v>
+        <v>79638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R30" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>79099</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R31" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3781,54 +3781,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>91493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3836,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R32" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,6 +3863,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3898,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734256</v>
+        <v>127734343</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3909,26 +3893,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3936,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686373</v>
+        <v>686366</v>
       </c>
       <c r="R33" t="n">
-        <v>7282022</v>
+        <v>7282024</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3980,7 +3981,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3999,32 +3999,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B34" t="n">
-        <v>91493</v>
+        <v>79638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R34" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734602</v>
+        <v>127734493</v>
       </c>
       <c r="B36" t="n">
         <v>57663</v>
@@ -4232,11 +4232,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4244,10 +4240,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686476</v>
+        <v>686286</v>
       </c>
       <c r="R36" t="n">
-        <v>7282298</v>
+        <v>7282001</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4280,6 +4276,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4306,7 +4307,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734493</v>
+        <v>127734602</v>
       </c>
       <c r="B37" t="n">
         <v>57663</v>
@@ -4337,7 +4338,11 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686286</v>
+        <v>686476</v>
       </c>
       <c r="R37" t="n">
-        <v>7282001</v>
+        <v>7282298</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4381,11 +4386,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>91499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R24" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B25" t="n">
-        <v>91493</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R25" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>78687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,43 +3367,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3411,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R28" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3449,17 +3432,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,26 +3468,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3516,10 +3512,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R29" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3554,13 +3550,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79638</v>
+        <v>79099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R30" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79099</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R31" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3784,7 +3784,7 @@
         <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,37 +4100,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734251</v>
+        <v>127734602</v>
       </c>
       <c r="B35" t="n">
-        <v>92626</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686434</v>
+        <v>686476</v>
       </c>
       <c r="R35" t="n">
-        <v>7282004</v>
+        <v>7282298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4182,7 +4187,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4307,42 +4311,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734602</v>
+        <v>127734251</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>92632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4350,10 +4349,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686476</v>
+        <v>686434</v>
       </c>
       <c r="R37" t="n">
-        <v>7282298</v>
+        <v>7282004</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4394,6 +4393,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B11" t="n">
-        <v>56855</v>
+        <v>97336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,46 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1688,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>97333</v>
+        <v>98480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1734,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>56858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,27 +1812,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127734510</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>127734354</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127734327</v>
       </c>
       <c r="B18" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>127734555</v>
       </c>
       <c r="B19" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127734518</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>127734420</v>
       </c>
       <c r="B21" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>127734344</v>
       </c>
       <c r="B22" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127734553</v>
       </c>
       <c r="B23" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>127734607</v>
       </c>
       <c r="B24" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127734349</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>127734329</v>
       </c>
       <c r="B26" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>127734640</v>
       </c>
       <c r="B27" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,37 +3781,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734539</v>
+        <v>127734343</v>
       </c>
       <c r="B32" t="n">
-        <v>91499</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3819,10 +3836,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686419</v>
+        <v>686366</v>
       </c>
       <c r="R32" t="n">
-        <v>7282238</v>
+        <v>7282024</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3863,7 +3880,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3882,54 +3898,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B33" t="n">
-        <v>57660</v>
+        <v>91502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3937,10 +3936,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R33" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3981,6 +3980,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>127734256</v>
       </c>
       <c r="B34" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>127734602</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>127734493</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>127734251</v>
       </c>
       <c r="B37" t="n">
-        <v>92632</v>
+        <v>92635</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4410,6 +4410,111 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128085433</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>500 m. öster Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>686357</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7281771</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127008809</v>
+        <v>128105832</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>78788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>7282172</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669651</v>
+        <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>97336</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,38 +1608,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R11" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1680,7 +1688,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1702,7 +1709,7 @@
         <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B13" t="n">
-        <v>56858</v>
+        <v>97344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,46 +1819,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R13" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127734510</v>
       </c>
       <c r="B16" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127734354</v>
+        <v>127734327</v>
       </c>
       <c r="B17" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686355</v>
+        <v>686366</v>
       </c>
       <c r="R17" t="n">
-        <v>7282009</v>
+        <v>7282026</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127734327</v>
+        <v>127734354</v>
       </c>
       <c r="B18" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686366</v>
+        <v>686355</v>
       </c>
       <c r="R18" t="n">
-        <v>7282026</v>
+        <v>7282009</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127734555</v>
+        <v>127734518</v>
       </c>
       <c r="B19" t="n">
-        <v>79641</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686452</v>
+        <v>686386</v>
       </c>
       <c r="R19" t="n">
-        <v>7282287</v>
+        <v>7282202</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127734518</v>
+        <v>127734555</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686386</v>
+        <v>686452</v>
       </c>
       <c r="R20" t="n">
-        <v>7282202</v>
+        <v>7282287</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2622,7 +2622,7 @@
         <v>127734420</v>
       </c>
       <c r="B21" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>127734344</v>
       </c>
       <c r="B22" t="n">
-        <v>78001</v>
+        <v>78007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127734553</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B24" t="n">
-        <v>91502</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R24" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B25" t="n">
-        <v>78782</v>
+        <v>91510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R25" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>127734329</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>127734640</v>
       </c>
       <c r="B27" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734343</v>
+        <v>127734256</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,43 +3792,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3836,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686366</v>
+        <v>686373</v>
       </c>
       <c r="R32" t="n">
-        <v>7282024</v>
+        <v>7282022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,6 +3863,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3898,37 +3882,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734539</v>
+        <v>127734343</v>
       </c>
       <c r="B33" t="n">
-        <v>91502</v>
+        <v>57669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3936,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686419</v>
+        <v>686366</v>
       </c>
       <c r="R33" t="n">
-        <v>7282238</v>
+        <v>7282024</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3980,7 +3981,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3999,32 +3999,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734256</v>
+        <v>127734539</v>
       </c>
       <c r="B34" t="n">
-        <v>79641</v>
+        <v>91510</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686373</v>
+        <v>686419</v>
       </c>
       <c r="R34" t="n">
-        <v>7282022</v>
+        <v>7282238</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4100,10 +4100,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734602</v>
+        <v>127734493</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4131,11 +4131,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4143,10 +4139,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686476</v>
+        <v>686286</v>
       </c>
       <c r="R35" t="n">
-        <v>7282298</v>
+        <v>7282001</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4179,6 +4175,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4205,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734493</v>
+        <v>127734602</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,7 +4237,11 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4244,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686286</v>
+        <v>686476</v>
       </c>
       <c r="R36" t="n">
-        <v>7282001</v>
+        <v>7282298</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4280,11 +4285,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4314,7 +4314,7 @@
         <v>127734251</v>
       </c>
       <c r="B37" t="n">
-        <v>92635</v>
+        <v>92643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,6 +4515,800 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128105828</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92643</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>686397</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7282144</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128105831</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>686356</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7281794</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128091983</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>686376</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7281751</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128105833</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>686295</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7281900</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128091984</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>686335</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7281697</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128105829</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>686519</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7282075</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128105830</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>686343</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7281765</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128091985</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79098</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>639</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grenlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Evernia mesomorpha</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>686337</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7281704</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669906</v>
+        <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>98488</v>
+        <v>97345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1741,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R12" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>97344</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,14 +1843,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R13" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127734327</v>
+        <v>127734354</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686366</v>
+        <v>686355</v>
       </c>
       <c r="R17" t="n">
-        <v>7282026</v>
+        <v>7282009</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127734354</v>
+        <v>127734327</v>
       </c>
       <c r="B18" t="n">
         <v>79647</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686355</v>
+        <v>686366</v>
       </c>
       <c r="R18" t="n">
-        <v>7282009</v>
+        <v>7282026</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127734518</v>
+        <v>127734555</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686386</v>
+        <v>686452</v>
       </c>
       <c r="R19" t="n">
-        <v>7282202</v>
+        <v>7282287</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127734555</v>
+        <v>127734518</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686452</v>
+        <v>686386</v>
       </c>
       <c r="R20" t="n">
-        <v>7282287</v>
+        <v>7282202</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>91511</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R24" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B25" t="n">
-        <v>91510</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R25" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B28" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,26 +3367,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3394,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R28" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3432,13 +3449,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3457,10 +3478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>78696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,43 +3489,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3512,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R29" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3550,17 +3554,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B30" t="n">
-        <v>79108</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R30" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>79108</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R31" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3882,54 +3882,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B33" t="n">
-        <v>57669</v>
+        <v>91511</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3937,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R33" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3981,6 +3964,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3999,37 +3983,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734539</v>
+        <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>91510</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4037,10 +4038,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686419</v>
+        <v>686366</v>
       </c>
       <c r="R34" t="n">
-        <v>7282238</v>
+        <v>7282024</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4081,7 +4082,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4100,38 +4100,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734493</v>
+        <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>92644</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4139,10 +4138,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686286</v>
+        <v>686434</v>
       </c>
       <c r="R35" t="n">
-        <v>7282001</v>
+        <v>7282004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4177,17 +4176,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4311,37 +4306,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734251</v>
+        <v>127734493</v>
       </c>
       <c r="B37" t="n">
-        <v>92643</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4349,10 +4345,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686434</v>
+        <v>686286</v>
       </c>
       <c r="R37" t="n">
-        <v>7282004</v>
+        <v>7282001</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4387,13 +4383,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>57776</v>
+        <v>78788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R42" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R43" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>78696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,43 +3367,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3411,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R28" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3449,17 +3432,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,26 +3468,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3516,10 +3512,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R29" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3554,13 +3550,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>79108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R30" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79108</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R31" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734256</v>
+        <v>127734343</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,26 +3792,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3819,10 +3836,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686373</v>
+        <v>686366</v>
       </c>
       <c r="R32" t="n">
-        <v>7282022</v>
+        <v>7282024</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3863,7 +3880,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3882,32 +3898,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B33" t="n">
-        <v>91511</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3936,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R33" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3983,54 +3999,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>91511</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4038,10 +4037,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R34" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4082,6 +4081,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B24" t="n">
-        <v>91511</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R24" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>91512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R25" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B30" t="n">
-        <v>79108</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R30" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>79108</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R31" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3781,54 +3781,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734343</v>
+        <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>57669</v>
+        <v>91512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3836,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686366</v>
+        <v>686419</v>
       </c>
       <c r="R32" t="n">
-        <v>7282024</v>
+        <v>7282238</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3880,6 +3863,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3999,37 +3983,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734539</v>
+        <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>91511</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4037,10 +4038,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686419</v>
+        <v>686366</v>
       </c>
       <c r="R34" t="n">
-        <v>7282238</v>
+        <v>7282024</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4081,7 +4082,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R42" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B43" t="n">
-        <v>57776</v>
+        <v>78788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R43" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127734555</v>
+        <v>127734518</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686452</v>
+        <v>686386</v>
       </c>
       <c r="R19" t="n">
-        <v>7282287</v>
+        <v>7282202</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127734518</v>
+        <v>127734555</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686386</v>
+        <v>686452</v>
       </c>
       <c r="R20" t="n">
-        <v>7282202</v>
+        <v>7282287</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>127734607</v>
       </c>
       <c r="B25" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734519</v>
+        <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>79108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,21 +3590,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686386</v>
+        <v>686467</v>
       </c>
       <c r="R30" t="n">
-        <v>7282202</v>
+        <v>7282303</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734610</v>
+        <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79108</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686467</v>
+        <v>686386</v>
       </c>
       <c r="R31" t="n">
-        <v>7282303</v>
+        <v>7282202</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3784,7 +3784,7 @@
         <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,37 +4100,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734251</v>
+        <v>127734493</v>
       </c>
       <c r="B35" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4138,10 +4139,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686434</v>
+        <v>686286</v>
       </c>
       <c r="R35" t="n">
-        <v>7282004</v>
+        <v>7282001</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4176,13 +4177,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4306,38 +4311,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734493</v>
+        <v>127734251</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>92646</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4345,10 +4349,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686286</v>
+        <v>686434</v>
       </c>
       <c r="R37" t="n">
-        <v>7282001</v>
+        <v>7282004</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4383,17 +4387,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>57776</v>
+        <v>78788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R42" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R43" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>97347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,46 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1688,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>97347</v>
+        <v>98491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1734,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,27 +1812,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -3781,32 +3781,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R32" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734256</v>
+        <v>127734539</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>91513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686373</v>
+        <v>686419</v>
       </c>
       <c r="R33" t="n">
-        <v>7282022</v>
+        <v>7282238</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734493</v>
+        <v>127734602</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4131,7 +4131,11 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4139,10 +4143,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686286</v>
+        <v>686476</v>
       </c>
       <c r="R35" t="n">
-        <v>7282001</v>
+        <v>7282298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4175,11 +4179,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4206,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734602</v>
+        <v>127734493</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4237,11 +4236,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4249,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686476</v>
+        <v>686286</v>
       </c>
       <c r="R36" t="n">
-        <v>7282298</v>
+        <v>7282001</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4285,6 +4280,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669651</v>
+        <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>97347</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,38 +1608,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R11" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1680,7 +1688,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669906</v>
+        <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>98491</v>
+        <v>97347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1734,14 +1741,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R12" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1801,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669842</v>
+        <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>56864</v>
+        <v>98491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,35 +1819,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -4100,42 +4100,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734602</v>
+        <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>92646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686476</v>
+        <v>686434</v>
       </c>
       <c r="R35" t="n">
-        <v>7282298</v>
+        <v>7282004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4187,6 +4182,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4205,7 +4201,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734493</v>
+        <v>127734602</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4236,7 +4232,11 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686286</v>
+        <v>686476</v>
       </c>
       <c r="R36" t="n">
-        <v>7282001</v>
+        <v>7282298</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4280,11 +4280,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4311,37 +4306,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734251</v>
+        <v>127734493</v>
       </c>
       <c r="B37" t="n">
-        <v>92646</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4349,10 +4345,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686434</v>
+        <v>686286</v>
       </c>
       <c r="R37" t="n">
-        <v>7282004</v>
+        <v>7282001</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4387,13 +4383,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>97347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,46 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1688,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>97347</v>
+        <v>98491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1734,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,27 +1812,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -4100,37 +4100,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734251</v>
+        <v>127734602</v>
       </c>
       <c r="B35" t="n">
-        <v>92646</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686434</v>
+        <v>686476</v>
       </c>
       <c r="R35" t="n">
-        <v>7282004</v>
+        <v>7282298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4182,7 +4187,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4201,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734602</v>
+        <v>127734493</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4232,11 +4236,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686476</v>
+        <v>686286</v>
       </c>
       <c r="R36" t="n">
-        <v>7282298</v>
+        <v>7282001</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4280,6 +4280,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4306,38 +4311,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734493</v>
+        <v>127734251</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>92646</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4345,10 +4349,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686286</v>
+        <v>686434</v>
       </c>
       <c r="R37" t="n">
-        <v>7282001</v>
+        <v>7282004</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4383,17 +4387,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>127669651</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>97347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,46 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1688,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>127669906</v>
       </c>
       <c r="B12" t="n">
-        <v>97347</v>
+        <v>98491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,14 +1734,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1808,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127669842</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,27 +1812,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,7 +1892,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -3781,32 +3781,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734256</v>
+        <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686373</v>
+        <v>686419</v>
       </c>
       <c r="R32" t="n">
-        <v>7282022</v>
+        <v>7282238</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B33" t="n">
-        <v>91513</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R33" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669651</v>
+        <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>97347</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,38 +1608,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686289</v>
+        <v>686599</v>
       </c>
       <c r="R11" t="n">
-        <v>7282027</v>
+        <v>7282017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1680,7 +1688,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669906</v>
+        <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>98491</v>
+        <v>97347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1734,14 +1741,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686599</v>
+        <v>686289</v>
       </c>
       <c r="R12" t="n">
-        <v>7282017</v>
+        <v>7282027</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1801,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669842</v>
+        <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>56864</v>
+        <v>98491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,35 +1819,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -3781,32 +3781,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R32" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734256</v>
+        <v>127734539</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>91513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686373</v>
+        <v>686419</v>
       </c>
       <c r="R33" t="n">
-        <v>7282022</v>
+        <v>7282238</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128105832</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>127669618</v>
       </c>
       <c r="B9" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127669528</v>
       </c>
       <c r="B10" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127669651</v>
       </c>
       <c r="B12" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127669906</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127669857</v>
       </c>
       <c r="B14" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>127670013</v>
       </c>
       <c r="B15" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127734510</v>
       </c>
       <c r="B16" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>127734354</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127734327</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127734518</v>
+        <v>127734555</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>79650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686386</v>
+        <v>686452</v>
       </c>
       <c r="R19" t="n">
-        <v>7282202</v>
+        <v>7282287</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127734555</v>
+        <v>127734518</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>78790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686452</v>
+        <v>686386</v>
       </c>
       <c r="R20" t="n">
-        <v>7282287</v>
+        <v>7282202</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2744,7 +2744,7 @@
         <v>127734344</v>
       </c>
       <c r="B22" t="n">
-        <v>78007</v>
+        <v>78010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127734553</v>
       </c>
       <c r="B23" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>127734349</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>127734607</v>
       </c>
       <c r="B25" t="n">
-        <v>91513</v>
+        <v>91521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>127734329</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>127734640</v>
       </c>
       <c r="B27" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B28" t="n">
-        <v>78696</v>
+        <v>57673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,26 +3367,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3394,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R28" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3432,13 +3449,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3457,10 +3478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>78699</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,43 +3489,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3512,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R29" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3550,17 +3554,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>127734256</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>127734539</v>
       </c>
       <c r="B33" t="n">
-        <v>91513</v>
+        <v>91521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734602</v>
+        <v>127734493</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,11 +4232,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4244,10 +4240,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686476</v>
+        <v>686286</v>
       </c>
       <c r="R36" t="n">
-        <v>7282298</v>
+        <v>7282001</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4280,6 +4276,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4306,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734493</v>
+        <v>127734602</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,7 +4338,11 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686286</v>
+        <v>686476</v>
       </c>
       <c r="R37" t="n">
-        <v>7282001</v>
+        <v>7282298</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4381,11 +4386,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4415,7 +4415,7 @@
         <v>128085433</v>
       </c>
       <c r="B38" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>128105829</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128105830</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128091985</v>
       </c>
       <c r="B46" t="n">
-        <v>79098</v>
+        <v>79101</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B42" t="n">
-        <v>78791</v>
+        <v>57777</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R42" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B43" t="n">
-        <v>57777</v>
+        <v>78791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R43" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128105832</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127734510</v>
       </c>
       <c r="B16" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>127734354</v>
       </c>
       <c r="B17" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127734327</v>
       </c>
       <c r="B18" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>127734555</v>
       </c>
       <c r="B19" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>127734518</v>
       </c>
       <c r="B20" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>127734420</v>
       </c>
       <c r="B21" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>127734344</v>
       </c>
       <c r="B22" t="n">
-        <v>78010</v>
+        <v>78055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127734553</v>
       </c>
       <c r="B23" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,32 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734349</v>
+        <v>127734607</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>91613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686355</v>
+        <v>686468</v>
       </c>
       <c r="R24" t="n">
-        <v>7282009</v>
+        <v>7282322</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,32 +3044,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734607</v>
+        <v>127734349</v>
       </c>
       <c r="B25" t="n">
-        <v>91521</v>
+        <v>78841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686468</v>
+        <v>686355</v>
       </c>
       <c r="R25" t="n">
-        <v>7282322</v>
+        <v>7282009</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>127734329</v>
       </c>
       <c r="B26" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>127734640</v>
       </c>
       <c r="B27" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734894</v>
+        <v>127734522</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>78749</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,43 +3367,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3411,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686422</v>
+        <v>686386</v>
       </c>
       <c r="R28" t="n">
-        <v>7282062</v>
+        <v>7282202</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3449,17 +3432,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734522</v>
+        <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>78699</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,26 +3468,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3516,10 +3512,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686386</v>
+        <v>686422</v>
       </c>
       <c r="R29" t="n">
-        <v>7282202</v>
+        <v>7282062</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3554,13 +3550,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>127734610</v>
       </c>
       <c r="B30" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127734519</v>
       </c>
       <c r="B31" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,32 +3781,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734256</v>
+        <v>127734539</v>
       </c>
       <c r="B32" t="n">
-        <v>79650</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686373</v>
+        <v>686419</v>
       </c>
       <c r="R32" t="n">
-        <v>7282022</v>
+        <v>7282238</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734539</v>
+        <v>127734256</v>
       </c>
       <c r="B33" t="n">
-        <v>91521</v>
+        <v>79702</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686419</v>
+        <v>686373</v>
       </c>
       <c r="R33" t="n">
-        <v>7282238</v>
+        <v>7282022</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>127734251</v>
       </c>
       <c r="B35" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>127734493</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>127734602</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128085433</v>
       </c>
       <c r="B38" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>128105833</v>
       </c>
       <c r="B42" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>128091984</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>128105829</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128105830</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128091985</v>
       </c>
       <c r="B46" t="n">
-        <v>79101</v>
+        <v>79152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5309,6 +5309,2053 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128119528</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>686383</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7282123</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128119539</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>686373</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7281650</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128119523</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>686527</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7282233</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128119538</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>686434</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7282302</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128119526</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>686377</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7281624</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128119542</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>686362</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7282108</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128119535</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>686420</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7282272</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128119537</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>686391</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7281718</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128119534</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>686397</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7281722</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128119532</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>658</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>686367</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7281634</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128119525</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90485</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>686388</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7282205</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128119527</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>686368</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7281629</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128119536</v>
+      </c>
+      <c r="B59" t="n">
+        <v>81068</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>686342</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7281699</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128119529</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>686491</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7282105</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128119541</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7281831</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128119524</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90485</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>686360</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7282114</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128119533</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92935</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>686367</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7282097</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128119540</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>686444</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7281922</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128119531</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>686385</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7282209</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128119530</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>686362</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7281845</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128119543</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>686384</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7282222</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>57789</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R42" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>78841</v>
+        <v>57789</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R43" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5311,32 +5311,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119528</v>
+        <v>128119539</v>
       </c>
       <c r="B47" t="n">
-        <v>92746</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686383</v>
+        <v>686373</v>
       </c>
       <c r="R47" t="n">
-        <v>7282123</v>
+        <v>7281650</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128119539</v>
+        <v>128119528</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>92746</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686373</v>
+        <v>686383</v>
       </c>
       <c r="R48" t="n">
-        <v>7281650</v>
+        <v>7282123</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128119535</v>
+        <v>128119537</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686420</v>
+        <v>686391</v>
       </c>
       <c r="R53" t="n">
-        <v>7282272</v>
+        <v>7281718</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128119537</v>
+        <v>128119535</v>
       </c>
       <c r="B54" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686391</v>
+        <v>686420</v>
       </c>
       <c r="R54" t="n">
-        <v>7281718</v>
+        <v>7282272</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119534</v>
+        <v>128119525</v>
       </c>
       <c r="B55" t="n">
-        <v>78841</v>
+        <v>90485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686397</v>
+        <v>686388</v>
       </c>
       <c r="R55" t="n">
-        <v>7281722</v>
+        <v>7282205</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6189,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119532</v>
+        <v>128119527</v>
       </c>
       <c r="B56" t="n">
-        <v>91748</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,21 +6200,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686367</v>
+        <v>686368</v>
       </c>
       <c r="R56" t="n">
-        <v>7281634</v>
+        <v>7281629</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6260,6 +6260,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6286,10 +6291,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119525</v>
+        <v>128119532</v>
       </c>
       <c r="B57" t="n">
-        <v>90485</v>
+        <v>91748</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6297,21 +6302,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6321,10 +6326,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686388</v>
+        <v>686367</v>
       </c>
       <c r="R57" t="n">
-        <v>7282205</v>
+        <v>7281634</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6383,10 +6388,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128119527</v>
+        <v>128119534</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>78841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6394,21 +6399,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6418,10 +6423,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686368</v>
+        <v>686397</v>
       </c>
       <c r="R58" t="n">
-        <v>7281629</v>
+        <v>7281722</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6454,11 +6459,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128105832</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128085433</v>
       </c>
       <c r="B38" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>128105829</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128105830</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>128091985</v>
       </c>
       <c r="B46" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119539</v>
+        <v>128119523</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79677</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686373</v>
+        <v>686527</v>
       </c>
       <c r="R47" t="n">
-        <v>7281650</v>
+        <v>7282233</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5411,7 +5411,7 @@
         <v>128119528</v>
       </c>
       <c r="B48" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128119523</v>
+        <v>128119539</v>
       </c>
       <c r="B49" t="n">
-        <v>79673</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686527</v>
+        <v>686373</v>
       </c>
       <c r="R49" t="n">
-        <v>7282233</v>
+        <v>7281650</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5605,7 +5605,7 @@
         <v>128119538</v>
       </c>
       <c r="B50" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>128119526</v>
       </c>
       <c r="B51" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>128119542</v>
       </c>
       <c r="B52" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>128119537</v>
       </c>
       <c r="B53" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>128119535</v>
       </c>
       <c r="B54" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119525</v>
+        <v>128119527</v>
       </c>
       <c r="B55" t="n">
-        <v>90485</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686388</v>
+        <v>686368</v>
       </c>
       <c r="R55" t="n">
-        <v>7282205</v>
+        <v>7281629</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6163,6 +6163,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6189,10 +6194,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119527</v>
+        <v>128119534</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>78845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,21 +6205,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6224,10 +6229,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686368</v>
+        <v>686397</v>
       </c>
       <c r="R56" t="n">
-        <v>7281629</v>
+        <v>7281722</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6260,11 +6265,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,7 +6294,7 @@
         <v>128119532</v>
       </c>
       <c r="B57" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128119534</v>
+        <v>128119525</v>
       </c>
       <c r="B58" t="n">
-        <v>78841</v>
+        <v>90497</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686397</v>
+        <v>686388</v>
       </c>
       <c r="R58" t="n">
-        <v>7281722</v>
+        <v>7282205</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6488,7 +6488,7 @@
         <v>128119536</v>
       </c>
       <c r="B59" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128119529</v>
       </c>
       <c r="B60" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128119541</v>
       </c>
       <c r="B61" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128119524</v>
       </c>
       <c r="B62" t="n">
-        <v>90485</v>
+        <v>90497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128119533</v>
       </c>
       <c r="B63" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>128119540</v>
       </c>
       <c r="B64" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>128119531</v>
       </c>
       <c r="B65" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>128119530</v>
       </c>
       <c r="B66" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>128119543</v>
       </c>
       <c r="B67" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -5311,32 +5311,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119523</v>
+        <v>128119528</v>
       </c>
       <c r="B47" t="n">
-        <v>79677</v>
+        <v>92758</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686527</v>
+        <v>686383</v>
       </c>
       <c r="R47" t="n">
-        <v>7282233</v>
+        <v>7282123</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128119528</v>
+        <v>128119539</v>
       </c>
       <c r="B48" t="n">
-        <v>92758</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686383</v>
+        <v>686373</v>
       </c>
       <c r="R48" t="n">
-        <v>7282123</v>
+        <v>7281650</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128119539</v>
+        <v>128119523</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686373</v>
+        <v>686527</v>
       </c>
       <c r="R49" t="n">
-        <v>7281650</v>
+        <v>7282233</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128119537</v>
+        <v>128119535</v>
       </c>
       <c r="B53" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686391</v>
+        <v>686420</v>
       </c>
       <c r="R53" t="n">
-        <v>7281718</v>
+        <v>7282272</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128119535</v>
+        <v>128119537</v>
       </c>
       <c r="B54" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686420</v>
+        <v>686391</v>
       </c>
       <c r="R54" t="n">
-        <v>7282272</v>
+        <v>7281718</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119527</v>
+        <v>128119532</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>91760</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686368</v>
+        <v>686367</v>
       </c>
       <c r="R55" t="n">
-        <v>7281629</v>
+        <v>7281634</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6163,11 +6163,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6194,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119534</v>
+        <v>128119525</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>90497</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,21 +6200,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686397</v>
+        <v>686388</v>
       </c>
       <c r="R56" t="n">
-        <v>7281722</v>
+        <v>7282205</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6291,10 +6286,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119532</v>
+        <v>128119527</v>
       </c>
       <c r="B57" t="n">
-        <v>91760</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6302,21 +6297,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6326,10 +6321,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686367</v>
+        <v>686368</v>
       </c>
       <c r="R57" t="n">
-        <v>7281634</v>
+        <v>7281629</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6362,6 +6357,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128119525</v>
+        <v>128119534</v>
       </c>
       <c r="B58" t="n">
-        <v>90497</v>
+        <v>78845</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686388</v>
+        <v>686397</v>
       </c>
       <c r="R58" t="n">
-        <v>7282205</v>
+        <v>7281722</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B42" t="n">
-        <v>78845</v>
+        <v>57793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R42" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B43" t="n">
-        <v>57793</v>
+        <v>78845</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R43" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5311,32 +5311,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119528</v>
+        <v>128119523</v>
       </c>
       <c r="B47" t="n">
-        <v>92758</v>
+        <v>79679</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686383</v>
+        <v>686527</v>
       </c>
       <c r="R47" t="n">
-        <v>7282123</v>
+        <v>7282233</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128119539</v>
+        <v>128119528</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>92760</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686373</v>
+        <v>686383</v>
       </c>
       <c r="R48" t="n">
-        <v>7281650</v>
+        <v>7282123</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128119523</v>
+        <v>128119539</v>
       </c>
       <c r="B49" t="n">
-        <v>79677</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686527</v>
+        <v>686373</v>
       </c>
       <c r="R49" t="n">
-        <v>7282233</v>
+        <v>7281650</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5605,7 +5605,7 @@
         <v>128119538</v>
       </c>
       <c r="B50" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>128119526</v>
       </c>
       <c r="B51" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>128119542</v>
       </c>
       <c r="B52" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128119535</v>
+        <v>128119537</v>
       </c>
       <c r="B53" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686420</v>
+        <v>686391</v>
       </c>
       <c r="R53" t="n">
-        <v>7282272</v>
+        <v>7281718</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128119537</v>
+        <v>128119535</v>
       </c>
       <c r="B54" t="n">
-        <v>78844</v>
+        <v>78847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686391</v>
+        <v>686420</v>
       </c>
       <c r="R54" t="n">
-        <v>7281718</v>
+        <v>7282272</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119532</v>
+        <v>128119525</v>
       </c>
       <c r="B55" t="n">
-        <v>91760</v>
+        <v>90499</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686367</v>
+        <v>686388</v>
       </c>
       <c r="R55" t="n">
-        <v>7281634</v>
+        <v>7282205</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6189,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119525</v>
+        <v>128119532</v>
       </c>
       <c r="B56" t="n">
-        <v>90497</v>
+        <v>91762</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,21 +6200,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686388</v>
+        <v>686367</v>
       </c>
       <c r="R56" t="n">
-        <v>7282205</v>
+        <v>7281634</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
         <v>128119534</v>
       </c>
       <c r="B58" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>128119536</v>
       </c>
       <c r="B59" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>128119529</v>
       </c>
       <c r="B60" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128119541</v>
       </c>
       <c r="B61" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128119524</v>
       </c>
       <c r="B62" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128119533</v>
       </c>
       <c r="B63" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>128119540</v>
       </c>
       <c r="B64" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>128119531</v>
       </c>
       <c r="B65" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>128119530</v>
       </c>
       <c r="B66" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>128119543</v>
       </c>
       <c r="B67" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128105832</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>128105828</v>
       </c>
       <c r="B39" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>128105831</v>
       </c>
       <c r="B40" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4808,48 +4808,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128105833</v>
+        <v>128091984</v>
       </c>
       <c r="B42" t="n">
-        <v>57793</v>
+        <v>78847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686295</v>
+        <v>686335</v>
       </c>
       <c r="R42" t="n">
-        <v>7281900</v>
+        <v>7281697</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4893,60 +4893,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128091984</v>
+        <v>128105833</v>
       </c>
       <c r="B43" t="n">
-        <v>78845</v>
+        <v>57793</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686335</v>
+        <v>686295</v>
       </c>
       <c r="R43" t="n">
-        <v>7281697</v>
+        <v>7281900</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
         <v>128091985</v>
       </c>
       <c r="B46" t="n">
-        <v>79156</v>
+        <v>79158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5311,32 +5311,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119523</v>
+        <v>128119528</v>
       </c>
       <c r="B47" t="n">
-        <v>79679</v>
+        <v>92760</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686527</v>
+        <v>686383</v>
       </c>
       <c r="R47" t="n">
-        <v>7282233</v>
+        <v>7282123</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5408,32 +5408,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128119528</v>
+        <v>128119539</v>
       </c>
       <c r="B48" t="n">
-        <v>92760</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686383</v>
+        <v>686373</v>
       </c>
       <c r="R48" t="n">
-        <v>7282123</v>
+        <v>7281650</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128119539</v>
+        <v>128119523</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79679</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686373</v>
+        <v>686527</v>
       </c>
       <c r="R49" t="n">
-        <v>7281650</v>
+        <v>7282233</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5699,32 +5699,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128119526</v>
+        <v>128119542</v>
       </c>
       <c r="B51" t="n">
-        <v>91466</v>
+        <v>92756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686377</v>
+        <v>686362</v>
       </c>
       <c r="R51" t="n">
-        <v>7281624</v>
+        <v>7282108</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5770,6 +5770,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5796,32 +5801,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128119542</v>
+        <v>128119526</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>91466</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5836,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686362</v>
+        <v>686377</v>
       </c>
       <c r="R52" t="n">
-        <v>7282108</v>
+        <v>7281624</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5867,11 +5872,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Häxring</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119525</v>
+        <v>128119534</v>
       </c>
       <c r="B55" t="n">
-        <v>90499</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686388</v>
+        <v>686397</v>
       </c>
       <c r="R55" t="n">
-        <v>7282205</v>
+        <v>7281722</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6286,10 +6286,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119527</v>
+        <v>128119525</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>90499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686368</v>
+        <v>686388</v>
       </c>
       <c r="R57" t="n">
-        <v>7281629</v>
+        <v>7282205</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6357,11 +6357,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6388,10 +6383,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128119534</v>
+        <v>128119527</v>
       </c>
       <c r="B58" t="n">
-        <v>78847</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6399,21 +6394,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6423,10 +6418,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686397</v>
+        <v>686368</v>
       </c>
       <c r="R58" t="n">
-        <v>7281722</v>
+        <v>7281629</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6459,6 +6454,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -5699,32 +5699,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128119542</v>
+        <v>128119526</v>
       </c>
       <c r="B51" t="n">
-        <v>92756</v>
+        <v>91466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686362</v>
+        <v>686377</v>
       </c>
       <c r="R51" t="n">
-        <v>7282108</v>
+        <v>7281624</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5770,11 +5770,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Häxring</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5801,32 +5796,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128119526</v>
+        <v>128119542</v>
       </c>
       <c r="B52" t="n">
-        <v>91466</v>
+        <v>92756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5836,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686377</v>
+        <v>686362</v>
       </c>
       <c r="R52" t="n">
-        <v>7281624</v>
+        <v>7282108</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5872,6 +5867,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119534</v>
+        <v>128119532</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>91762</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686397</v>
+        <v>686367</v>
       </c>
       <c r="R55" t="n">
-        <v>7281722</v>
+        <v>7281634</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6189,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119532</v>
+        <v>128119525</v>
       </c>
       <c r="B56" t="n">
-        <v>91762</v>
+        <v>90499</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,21 +6200,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686367</v>
+        <v>686388</v>
       </c>
       <c r="R56" t="n">
-        <v>7281634</v>
+        <v>7282205</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6286,10 +6286,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119525</v>
+        <v>128119534</v>
       </c>
       <c r="B57" t="n">
-        <v>90499</v>
+        <v>78847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686388</v>
+        <v>686397</v>
       </c>
       <c r="R57" t="n">
-        <v>7282205</v>
+        <v>7281722</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -5314,7 +5314,7 @@
         <v>128119528</v>
       </c>
       <c r="B47" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>128119538</v>
       </c>
       <c r="B50" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5699,32 +5699,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128119526</v>
+        <v>128119542</v>
       </c>
       <c r="B51" t="n">
-        <v>91466</v>
+        <v>92757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686377</v>
+        <v>686362</v>
       </c>
       <c r="R51" t="n">
-        <v>7281624</v>
+        <v>7282108</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5770,6 +5770,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5796,32 +5801,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128119542</v>
+        <v>128119526</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>91467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5836,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686362</v>
+        <v>686377</v>
       </c>
       <c r="R52" t="n">
-        <v>7282108</v>
+        <v>7281624</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5867,11 +5872,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Häxring</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6092,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119532</v>
+        <v>128119534</v>
       </c>
       <c r="B55" t="n">
-        <v>91762</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686367</v>
+        <v>686397</v>
       </c>
       <c r="R55" t="n">
-        <v>7281634</v>
+        <v>7281722</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6286,10 +6286,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119534</v>
+        <v>128119532</v>
       </c>
       <c r="B57" t="n">
-        <v>78847</v>
+        <v>91763</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686397</v>
+        <v>686367</v>
       </c>
       <c r="R57" t="n">
-        <v>7281722</v>
+        <v>7281634</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6585,7 +6585,7 @@
         <v>128119529</v>
       </c>
       <c r="B60" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>128119541</v>
       </c>
       <c r="B61" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>128119533</v>
       </c>
       <c r="B63" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>128119540</v>
       </c>
       <c r="B64" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>128119531</v>
       </c>
       <c r="B65" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>128119530</v>
       </c>
       <c r="B66" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>128119543</v>
       </c>
       <c r="B67" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7356,6 +7356,685 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129319670</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>686183</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7282312</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129319676</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78796</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>686187</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7282173</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129319677</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91701</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>686205</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7282271</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129319673</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92450</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>686373</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7282185</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129319678</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78442</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>686195</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7282273</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129319669</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>686164</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7282243</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129319674</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93029</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svärdåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>686412</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7282314</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92452</v>
+        <v>92466</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92466</v>
+        <v>92467</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92467</v>
+        <v>92470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92470</v>
+        <v>92472</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92472</v>
+        <v>92476</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92477</v>
+        <v>92480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91603</v>
+        <v>91606</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92480</v>
+        <v>92508</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91606</v>
+        <v>91634</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92508</v>
+        <v>92514</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92514</v>
+        <v>92515</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91640</v>
+        <v>91641</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -7361,7 +7361,7 @@
         <v>129319670</v>
       </c>
       <c r="B68" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129319676</v>
       </c>
       <c r="B69" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129319677</v>
       </c>
       <c r="B70" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129319673</v>
       </c>
       <c r="B71" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129319678</v>
       </c>
       <c r="B72" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129319669</v>
       </c>
       <c r="B73" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129319674</v>
       </c>
       <c r="B74" t="n">
-        <v>91641</v>
+        <v>91646</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127008805</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127008810</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127008812</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127008808</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,45 +1184,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>127008813</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686284</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1263,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gammal</t>
+          <t>bohål i sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,49 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>127008811</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686427</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7282203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i sälg</t>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,6 +1374,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>57073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>56880</v>
+        <v>57073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57682</v>
+        <v>57881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>127669842</v>
       </c>
       <c r="B11" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127734894</v>
       </c>
       <c r="B29" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127734343</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128091983</v>
       </c>
       <c r="B41" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20996-2025 artfynd.xlsx
+++ b/artfynd/A 20996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127008805</v>
+        <v>129319676</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686321</v>
+        <v>686187</v>
       </c>
       <c r="R2" t="n">
-        <v>7281921</v>
+        <v>7282173</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127008810</v>
+        <v>129319669</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>79917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686303</v>
+        <v>686164</v>
       </c>
       <c r="R3" t="n">
-        <v>7281986</v>
+        <v>7282243</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127008812</v>
+        <v>129319670</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>79917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686480</v>
+        <v>686183</v>
       </c>
       <c r="R4" t="n">
-        <v>7282249</v>
+        <v>7282312</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -943,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gammal</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105832</v>
+        <v>127734510</v>
       </c>
       <c r="B5" t="n">
-        <v>78847</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686430</v>
+        <v>686360</v>
       </c>
       <c r="R5" t="n">
-        <v>7282172</v>
+        <v>7282102</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,12 +1034,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,28 +1048,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127008808</v>
+        <v>127734522</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,41 +1078,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686271</v>
+        <v>686386</v>
       </c>
       <c r="R6" t="n">
-        <v>7281944</v>
+        <v>7282202</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,17 +1135,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,66 +1149,74 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127008811</v>
+        <v>128085114</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>79396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>639</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686427</v>
+        <v>686329</v>
       </c>
       <c r="R7" t="n">
-        <v>7282203</v>
+        <v>7281700</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1249,17 +1240,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>gammal</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,64 +1261,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127008813</v>
+        <v>128091985</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>79396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>639</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686284</v>
+        <v>686337</v>
       </c>
       <c r="R8" t="n">
-        <v>7281995</v>
+        <v>7281704</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1356,17 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>bohål i sälg</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,64 +1358,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127669618</v>
+        <v>128119532</v>
       </c>
       <c r="B9" t="n">
-        <v>98499</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686291</v>
+        <v>686367</v>
       </c>
       <c r="R9" t="n">
-        <v>7282051</v>
+        <v>7281634</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,12 +1435,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,71 +1449,69 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127669528</v>
+        <v>127734610</v>
       </c>
       <c r="B10" t="n">
-        <v>98499</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686299</v>
+        <v>686467</v>
       </c>
       <c r="R10" t="n">
-        <v>7282083</v>
+        <v>7282303</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1564,12 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,72 +1556,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127669842</v>
+        <v>128119536</v>
       </c>
       <c r="B11" t="n">
-        <v>57092</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686599</v>
+        <v>686342</v>
       </c>
       <c r="R11" t="n">
-        <v>7282017</v>
+        <v>7281699</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,12 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,64 +1653,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127669651</v>
+        <v>128119526</v>
       </c>
       <c r="B12" t="n">
-        <v>97355</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>500m. öster Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686289</v>
+        <v>686377</v>
       </c>
       <c r="R12" t="n">
-        <v>7282027</v>
+        <v>7281624</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1775,12 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,71 +1744,69 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127669906</v>
+        <v>127734539</v>
       </c>
       <c r="B13" t="n">
-        <v>98499</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686599</v>
+        <v>686419</v>
       </c>
       <c r="R13" t="n">
-        <v>7282017</v>
+        <v>7282238</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,12 +1830,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,64 +1851,63 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127669857</v>
+        <v>127734607</v>
       </c>
       <c r="B14" t="n">
-        <v>98395</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686599</v>
+        <v>686468</v>
       </c>
       <c r="R14" t="n">
-        <v>7282017</v>
+        <v>7282322</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1979,12 +1931,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,64 +1952,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670013</v>
+        <v>128119538</v>
       </c>
       <c r="B15" t="n">
-        <v>98395</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686544</v>
+        <v>686434</v>
       </c>
       <c r="R15" t="n">
-        <v>7282153</v>
+        <v>7282302</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2081,12 +2029,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,67 +2043,63 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127734510</v>
+        <v>129319677</v>
       </c>
       <c r="B16" t="n">
-        <v>78749</v>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686360</v>
+        <v>686205</v>
       </c>
       <c r="R16" t="n">
-        <v>7282102</v>
+        <v>7282271</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2182,12 +2126,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,29 +2140,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127734354</v>
+        <v>128119524</v>
       </c>
       <c r="B17" t="n">
-        <v>79702</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,37 +2169,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686355</v>
+        <v>686360</v>
       </c>
       <c r="R17" t="n">
-        <v>7282009</v>
+        <v>7282114</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2283,12 +2223,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,29 +2237,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127734327</v>
+        <v>128119525</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,37 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686366</v>
+        <v>686388</v>
       </c>
       <c r="R18" t="n">
-        <v>7282026</v>
+        <v>7282205</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,12 +2320,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,29 +2334,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127734555</v>
+        <v>128105831</v>
       </c>
       <c r="B19" t="n">
-        <v>79702</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,37 +2363,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686452</v>
+        <v>686356</v>
       </c>
       <c r="R19" t="n">
-        <v>7282287</v>
+        <v>7281794</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2485,12 +2417,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,29 +2431,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127734518</v>
+        <v>128119533</v>
       </c>
       <c r="B20" t="n">
-        <v>78840</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,37 +2460,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686386</v>
+        <v>686367</v>
       </c>
       <c r="R20" t="n">
-        <v>7282202</v>
+        <v>7282097</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2586,12 +2514,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2600,84 +2528,63 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127734420</v>
+        <v>129319674</v>
       </c>
       <c r="B21" t="n">
-        <v>56876</v>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686309</v>
+        <v>686412</v>
       </c>
       <c r="R21" t="n">
-        <v>7282011</v>
+        <v>7282314</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2704,17 +2611,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Den kvarvarande naturskogsresten är lämplig tjäderbiotop och tjäderhonan är troligen stationär i området. Dessutom är miljön kring källbäcken lämpligt för häckning och uppfödande av tjäderkycklingar.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,22 +2631,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127734344</v>
+        <v>127008811</v>
       </c>
       <c r="B22" t="n">
-        <v>78055</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,40 +2654,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686366</v>
+        <v>686427</v>
       </c>
       <c r="R22" t="n">
-        <v>7282024</v>
+        <v>7282203</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2809,12 +2708,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,22 +2734,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127734553</v>
+        <v>127008812</v>
       </c>
       <c r="B23" t="n">
-        <v>78840</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,40 +2757,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686452</v>
+        <v>686480</v>
       </c>
       <c r="R23" t="n">
-        <v>7282287</v>
+        <v>7282249</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2910,12 +2811,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>gammal</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2931,60 +2837,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127734607</v>
+        <v>128119540</v>
       </c>
       <c r="B24" t="n">
-        <v>91613</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686468</v>
+        <v>686444</v>
       </c>
       <c r="R24" t="n">
-        <v>7282322</v>
+        <v>7281922</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3011,12 +2914,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,29 +2928,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127734349</v>
+        <v>128119541</v>
       </c>
       <c r="B25" t="n">
-        <v>78841</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,37 +2957,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686355</v>
+        <v>686366</v>
       </c>
       <c r="R25" t="n">
-        <v>7282009</v>
+        <v>7281831</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3112,12 +3011,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3126,29 +3025,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127734329</v>
+        <v>128119542</v>
       </c>
       <c r="B26" t="n">
-        <v>78840</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,37 +3054,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686366</v>
+        <v>686362</v>
       </c>
       <c r="R26" t="n">
-        <v>7282026</v>
+        <v>7282108</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3213,12 +3108,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3227,72 +3127,63 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127734640</v>
+        <v>128119543</v>
       </c>
       <c r="B27" t="n">
-        <v>57789</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>686342</v>
+        <v>686384</v>
       </c>
       <c r="R27" t="n">
-        <v>7281946</v>
+        <v>7282222</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3319,17 +3210,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>En familjegrupp med 4 fåglar</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3344,44 +3230,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127734522</v>
+        <v>127734251</v>
       </c>
       <c r="B28" t="n">
-        <v>78749</v>
+        <v>93201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3280,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686386</v>
+        <v>686434</v>
       </c>
       <c r="R28" t="n">
-        <v>7282202</v>
+        <v>7282004</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3457,65 +3343,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127734894</v>
+        <v>128105828</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>93201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686422</v>
+        <v>686397</v>
       </c>
       <c r="R29" t="n">
-        <v>7282062</v>
+        <v>7282144</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3542,17 +3408,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En hane i sitt revir respektive del av reviret</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3567,60 +3428,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127734610</v>
+        <v>128119528</v>
       </c>
       <c r="B30" t="n">
-        <v>79162</v>
+        <v>93201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686467</v>
+        <v>686383</v>
       </c>
       <c r="R30" t="n">
-        <v>7282303</v>
+        <v>7282123</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3647,12 +3505,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3661,67 +3519,63 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734519</v>
+        <v>128119529</v>
       </c>
       <c r="B31" t="n">
-        <v>79702</v>
+        <v>93201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686386</v>
+        <v>686491</v>
       </c>
       <c r="R31" t="n">
-        <v>7282202</v>
+        <v>7282105</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3748,12 +3602,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3762,29 +3616,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127734539</v>
+        <v>128119530</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>93201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,37 +3645,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686419</v>
+        <v>686362</v>
       </c>
       <c r="R32" t="n">
-        <v>7282238</v>
+        <v>7281845</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3849,12 +3699,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3863,67 +3713,63 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734256</v>
+        <v>128119531</v>
       </c>
       <c r="B33" t="n">
-        <v>79702</v>
+        <v>93201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686373</v>
+        <v>686385</v>
       </c>
       <c r="R33" t="n">
-        <v>7282022</v>
+        <v>7282209</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3950,12 +3796,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3964,29 +3810,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734343</v>
+        <v>129319673</v>
       </c>
       <c r="B34" t="n">
-        <v>57901</v>
+        <v>92841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3994,54 +3839,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686366</v>
+        <v>686373</v>
       </c>
       <c r="R34" t="n">
-        <v>7282024</v>
+        <v>7282185</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4068,12 +3893,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4088,22 +3913,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127734251</v>
+        <v>128119539</v>
       </c>
       <c r="B35" t="n">
-        <v>92746</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4111,37 +3936,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686434</v>
+        <v>686373</v>
       </c>
       <c r="R35" t="n">
-        <v>7282004</v>
+        <v>7281650</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4168,12 +3990,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4182,29 +4004,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127734493</v>
+        <v>129319678</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>78730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4212,38 +4033,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Arvidsjaur-Svärdåive, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686286</v>
+        <v>686195</v>
       </c>
       <c r="R36" t="n">
-        <v>7282001</v>
+        <v>7282273</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4270,17 +4087,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ett bohål i en sälg vid källbäcken.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,22 +4107,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127734602</v>
+        <v>127734329</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,31 +4130,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4350,10 +4157,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686476</v>
+        <v>686366</v>
       </c>
       <c r="R37" t="n">
-        <v>7282298</v>
+        <v>7282026</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4394,6 +4201,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4412,56 +4220,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128085433</v>
+        <v>127734518</v>
       </c>
       <c r="B38" t="n">
-        <v>57793</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>500 m. öster Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686357</v>
+        <v>686386</v>
       </c>
       <c r="R38" t="n">
-        <v>7281771</v>
+        <v>7282202</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4485,12 +4288,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4499,63 +4302,67 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128105828</v>
+        <v>127734553</v>
       </c>
       <c r="B39" t="n">
-        <v>92760</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686397</v>
+        <v>686452</v>
       </c>
       <c r="R39" t="n">
-        <v>7282144</v>
+        <v>7282287</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4582,12 +4389,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4596,28 +4403,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128105831</v>
+        <v>128119537</v>
       </c>
       <c r="B40" t="n">
-        <v>92949</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4625,34 +4433,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686356</v>
+        <v>686391</v>
       </c>
       <c r="R40" t="n">
-        <v>7281794</v>
+        <v>7281718</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4699,60 +4507,63 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128091983</v>
+        <v>127734256</v>
       </c>
       <c r="B41" t="n">
-        <v>57092</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686376</v>
+        <v>686373</v>
       </c>
       <c r="R41" t="n">
-        <v>7281751</v>
+        <v>7282022</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4776,12 +4587,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4790,28 +4601,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128091984</v>
+        <v>127734327</v>
       </c>
       <c r="B42" t="n">
-        <v>78847</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4819,37 +4631,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686335</v>
+        <v>686366</v>
       </c>
       <c r="R42" t="n">
-        <v>7281697</v>
+        <v>7282026</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4873,12 +4688,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,63 +4702,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128105833</v>
+        <v>127734354</v>
       </c>
       <c r="B43" t="n">
-        <v>57793</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686295</v>
+        <v>686355</v>
       </c>
       <c r="R43" t="n">
-        <v>7281900</v>
+        <v>7282009</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4970,12 +4789,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4984,28 +4803,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128105829</v>
+        <v>127734519</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,38 +4833,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686519</v>
+        <v>686386</v>
       </c>
       <c r="R44" t="n">
-        <v>7282075</v>
+        <v>7282202</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5071,17 +4890,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5090,28 +4904,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128105830</v>
+        <v>127734555</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5119,38 +4934,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686343</v>
+        <v>686452</v>
       </c>
       <c r="R45" t="n">
-        <v>7281765</v>
+        <v>7282287</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5177,17 +4991,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5196,66 +5005,70 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128091985</v>
+        <v>127734344</v>
       </c>
       <c r="B46" t="n">
-        <v>79158</v>
+        <v>78334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>639</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686337</v>
+        <v>686366</v>
       </c>
       <c r="R46" t="n">
-        <v>7281704</v>
+        <v>7282024</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5279,12 +5092,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5293,63 +5106,84 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128119528</v>
+        <v>127734343</v>
       </c>
       <c r="B47" t="n">
-        <v>92761</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686383</v>
+        <v>686366</v>
       </c>
       <c r="R47" t="n">
-        <v>7282123</v>
+        <v>7282024</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5376,12 +5210,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,22 +5230,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128119539</v>
+        <v>127008805</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,37 +5253,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686373</v>
+        <v>686321</v>
       </c>
       <c r="R48" t="n">
-        <v>7281650</v>
+        <v>7281921</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5473,12 +5311,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,22 +5336,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128119523</v>
+        <v>127008808</v>
       </c>
       <c r="B49" t="n">
-        <v>79679</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,37 +5359,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686527</v>
+        <v>686271</v>
       </c>
       <c r="R49" t="n">
-        <v>7282233</v>
+        <v>7281944</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5570,12 +5417,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5590,57 +5442,61 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128119538</v>
+        <v>127734493</v>
       </c>
       <c r="B50" t="n">
-        <v>91628</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>686434</v>
+        <v>686286</v>
       </c>
       <c r="R50" t="n">
-        <v>7282302</v>
+        <v>7282001</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5667,12 +5523,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ett bohål i en sälg vid källbäcken.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5687,57 +5548,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128119542</v>
+        <v>127734602</v>
       </c>
       <c r="B51" t="n">
-        <v>92757</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686362</v>
+        <v>686476</v>
       </c>
       <c r="R51" t="n">
-        <v>7282108</v>
+        <v>7282298</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5764,17 +5633,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Häxring</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5789,22 +5653,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128119526</v>
+        <v>127734894</v>
       </c>
       <c r="B52" t="n">
-        <v>91467</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5812,34 +5676,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686377</v>
+        <v>686422</v>
       </c>
       <c r="R52" t="n">
-        <v>7281624</v>
+        <v>7282062</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5866,12 +5750,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>En hane i sitt revir respektive del av reviret</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5886,22 +5775,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128119537</v>
+        <v>128105829</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,34 +5798,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686391</v>
+        <v>686519</v>
       </c>
       <c r="R53" t="n">
-        <v>7281718</v>
+        <v>7282075</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5971,6 +5864,11 @@
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5983,22 +5881,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128119535</v>
+        <v>128105830</v>
       </c>
       <c r="B54" t="n">
-        <v>78847</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,34 +5904,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686420</v>
+        <v>686343</v>
       </c>
       <c r="R54" t="n">
-        <v>7282272</v>
+        <v>7281765</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6068,6 +5970,11 @@
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6080,22 +5987,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128119534</v>
+        <v>128119527</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,21 +6010,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6127,10 +6034,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686397</v>
+        <v>686368</v>
       </c>
       <c r="R55" t="n">
-        <v>7281722</v>
+        <v>7281629</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6163,6 +6070,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6189,48 +6101,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128119525</v>
+        <v>127669842</v>
       </c>
       <c r="B56" t="n">
-        <v>90499</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686388</v>
+        <v>686599</v>
       </c>
       <c r="R56" t="n">
-        <v>7282205</v>
+        <v>7282017</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6254,12 +6178,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6274,57 +6198,77 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128119532</v>
+        <v>127734420</v>
       </c>
       <c r="B57" t="n">
-        <v>91763</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686367</v>
+        <v>686309</v>
       </c>
       <c r="R57" t="n">
-        <v>7281634</v>
+        <v>7282011</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6351,12 +6295,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Den kvarvarande naturskogsresten är lämplig tjäderbiotop och tjäderhonan är troligen stationär i området. Dessutom är miljön kring källbäcken lämpligt för häckning och uppfödande av tjäderkycklingar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6371,60 +6320,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128119527</v>
+        <v>128091983</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686368</v>
+        <v>686376</v>
       </c>
       <c r="R58" t="n">
-        <v>7281629</v>
+        <v>7281751</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6454,11 +6403,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gammalt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6473,22 +6417,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128119536</v>
+        <v>127734640</v>
       </c>
       <c r="B59" t="n">
-        <v>81074</v>
+        <v>58057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6496,34 +6440,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>686342</v>
       </c>
       <c r="R59" t="n">
-        <v>7281699</v>
+        <v>7281946</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6550,12 +6502,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>En familjegrupp med 4 fåglar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6570,60 +6527,68 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128119529</v>
+        <v>128085433</v>
       </c>
       <c r="B60" t="n">
-        <v>92761</v>
+        <v>58057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>686491</v>
+        <v>686357</v>
       </c>
       <c r="R60" t="n">
-        <v>7282105</v>
+        <v>7281771</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6667,57 +6632,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128119541</v>
+        <v>128105833</v>
       </c>
       <c r="B61" t="n">
-        <v>92757</v>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686366</v>
+        <v>686295</v>
       </c>
       <c r="R61" t="n">
-        <v>7281831</v>
+        <v>7281900</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6764,22 +6729,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128119524</v>
+        <v>129319675</v>
       </c>
       <c r="B62" t="n">
-        <v>90499</v>
+        <v>58057</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6787,34 +6752,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>686360</v>
+        <v>686618</v>
       </c>
       <c r="R62" t="n">
-        <v>7282114</v>
+        <v>7282260</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6841,12 +6806,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6861,22 +6826,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128119533</v>
+        <v>127670020</v>
       </c>
       <c r="B63" t="n">
-        <v>92950</v>
+        <v>29424</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6884,37 +6849,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>103271</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tajgahumla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bombus cingulatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Wahlberg, 1855</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>686367</v>
+        <v>686544</v>
       </c>
       <c r="R63" t="n">
-        <v>7282097</v>
+        <v>7282153</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6938,12 +6908,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6952,28 +6922,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128119540</v>
+        <v>127669857</v>
       </c>
       <c r="B64" t="n">
-        <v>92757</v>
+        <v>99035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6981,37 +6952,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>686444</v>
+        <v>686599</v>
       </c>
       <c r="R64" t="n">
-        <v>7281922</v>
+        <v>7282017</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7035,12 +7010,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7049,66 +7024,71 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128119531</v>
+        <v>127670013</v>
       </c>
       <c r="B65" t="n">
-        <v>92761</v>
+        <v>99035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>686385</v>
+        <v>686544</v>
       </c>
       <c r="R65" t="n">
-        <v>7282209</v>
+        <v>7282153</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7132,12 +7112,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7146,66 +7126,71 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128119530</v>
+        <v>127669651</v>
       </c>
       <c r="B66" t="n">
-        <v>92761</v>
+        <v>97983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4365</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>686362</v>
+        <v>686289</v>
       </c>
       <c r="R66" t="n">
-        <v>7281845</v>
+        <v>7282027</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7229,12 +7214,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7243,28 +7228,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128119543</v>
+        <v>127669528</v>
       </c>
       <c r="B67" t="n">
-        <v>92757</v>
+        <v>99140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7272,37 +7258,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svärdåive kroktjärnarna, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>686384</v>
+        <v>686299</v>
       </c>
       <c r="R67" t="n">
-        <v>7282222</v>
+        <v>7282083</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7326,12 +7316,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7340,66 +7330,71 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319670</v>
+        <v>127669618</v>
       </c>
       <c r="B68" t="n">
-        <v>79671</v>
+        <v>99140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>500m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>686183</v>
+        <v>686291</v>
       </c>
       <c r="R68" t="n">
-        <v>7282312</v>
+        <v>7282051</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7423,12 +7418,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7437,66 +7432,71 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319676</v>
+        <v>127669906</v>
       </c>
       <c r="B69" t="n">
-        <v>78838</v>
+        <v>99140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>500 m. öster Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>686187</v>
+        <v>686599</v>
       </c>
       <c r="R69" t="n">
-        <v>7282173</v>
+        <v>7282017</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7534,50 +7534,51 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319677</v>
+        <v>128105832</v>
       </c>
       <c r="B70" t="n">
-        <v>91766</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7587,10 +7588,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>686205</v>
+        <v>686430</v>
       </c>
       <c r="R70" t="n">
-        <v>7282271</v>
+        <v>7282172</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7617,12 +7618,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7649,10 +7650,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319673</v>
+        <v>127734349</v>
       </c>
       <c r="B71" t="n">
-        <v>92520</v>
+        <v>79085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,34 +7661,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4745</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur-Svärdåive, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>686373</v>
+        <v>686355</v>
       </c>
       <c r="R71" t="n">
-        <v>7282185</v>
+        <v>7282009</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7714,12 +7718,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7728,28 +7732,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319678</v>
+        <v>128091984</v>
       </c>
       <c r="B72" t="n">
-        <v>78484</v>
+        <v>79085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7757,37 +7762,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>686195</v>
+        <v>686335</v>
       </c>
       <c r="R72" t="n">
-        <v>7282273</v>
+        <v>7281697</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7811,12 +7816,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7831,22 +7836,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319669</v>
+        <v>128119534</v>
       </c>
       <c r="B73" t="n">
-        <v>79671</v>
+        <v>79085</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,34 +7859,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686164</v>
+        <v>686397</v>
       </c>
       <c r="R73" t="n">
-        <v>7282243</v>
+        <v>7281722</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7908,12 +7913,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7928,22 +7933,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319674</v>
+        <v>128119535</v>
       </c>
       <c r="B74" t="n">
-        <v>91646</v>
+        <v>79085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,34 +7956,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svärdåive, Pi lm</t>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686412</v>
+        <v>686420</v>
       </c>
       <c r="R74" t="n">
-        <v>7282314</v>
+        <v>7282272</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8005,12 +8010,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8025,15 +8030,112 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128119523</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svärdåive kroktjärnarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>686527</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7282233</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
